--- a/Result/profitability/5353.xlsx
+++ b/Result/profitability/5353.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.15</v>
       </c>
       <c r="M2" t="n">
-        <v>0.35</v>
+        <v>0.32375</v>
       </c>
       <c r="N2" t="n">
-        <v>23.2625</v>
+        <v>22.85125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.06</v>
       </c>
       <c r="M3" t="n">
-        <v>0.26</v>
+        <v>0.265</v>
       </c>
       <c r="N3" t="n">
-        <v>21.23375</v>
+        <v>20.88875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0.24625</v>
+        <v>0.23625</v>
       </c>
       <c r="N4" t="n">
-        <v>19.62375</v>
+        <v>19.495</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0.21125</v>
+        <v>0.27125</v>
       </c>
       <c r="N5" t="n">
-        <v>18.7525</v>
+        <v>19.02125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.22125</v>
+        <v>0.215</v>
       </c>
       <c r="N6" t="n">
-        <v>17.91</v>
+        <v>17.88875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.155</v>
+        <v>0.16375</v>
       </c>
       <c r="N7" t="n">
-        <v>16.39</v>
+        <v>16.32375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.09</v>
       </c>
       <c r="M8" t="n">
-        <v>0.11875</v>
+        <v>0.1125</v>
       </c>
       <c r="N8" t="n">
-        <v>14.91625</v>
+        <v>14.705</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.2</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08124999999999999</v>
+        <v>0.08125</v>
       </c>
       <c r="N9" t="n">
         <v>12.97</v>
@@ -1645,7 +1645,7 @@
         <v>-0.22</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0725</v>
+        <v>0.07250000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>12.245</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5353</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>503</v>
+      </c>
+      <c r="D75" t="n">
+        <v>383</v>
+      </c>
+      <c r="E75" t="n">
+        <v>119</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23.73</v>
+      </c>
+      <c r="G75" t="n">
+        <v>26</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.10%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>11</v>
+      </c>
+      <c r="J75" t="n">
+        <v>36</v>
+      </c>
+      <c r="K75" t="n">
+        <v>34</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24.645</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.04999999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.09999999999999998</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.690000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.06648308418568061</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.150000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.09962928637627444</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
